--- a/20260514_银河.xlsx
+++ b/20260514_银河.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>713.8</v>
+        <v>705.8</v>
       </c>
       <c r="D2" s="1">
-        <v>-5.8</v>
+        <v>-13.8</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.0081</v>
+        <v>-0.0192</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,16 +553,16 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>2.7</v>
+        <v>-5.3</v>
       </c>
       <c r="K2" s="2">
-        <v>0.0038</v>
+        <v>-0.0075</v>
       </c>
       <c r="L2" s="1">
-        <v>2.7</v>
+        <v>-5.3</v>
       </c>
       <c r="M2" s="2">
-        <v>0.0038</v>
+        <v>-0.0075</v>
       </c>
       <c r="N2" s="1">
         <v>2.3</v>
@@ -574,7 +574,7 @@
         <v>2.3</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.024</v>
+        <v>0.0239</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,28 +583,28 @@
         <v>4</v>
       </c>
       <c r="T2" s="2">
-        <v>-0.0081</v>
+        <v>-0.0192</v>
       </c>
       <c r="U2" s="5">
-        <v>3.569</v>
+        <v>3.529</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v/>
+        <v>0.0077</v>
       </c>
       <c r="X2" s="2">
-        <v>0.1108</v>
+        <v>0.0983</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0865</v>
+        <v>0.0743</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1748</v>
+        <v>0.1616</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4677</v>
+        <v>0.4512</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>866.8</v>
+        <v>857.6</v>
       </c>
       <c r="D3" s="1">
-        <v>2.4</v>
+        <v>-6.8</v>
       </c>
       <c r="E3" s="2">
-        <v>0.0028</v>
+        <v>-0.0079</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,16 +636,16 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>3.9</v>
+        <v>-5.3</v>
       </c>
       <c r="K3" s="2">
-        <v>0.0045</v>
+        <v>-0.0061</v>
       </c>
       <c r="L3" s="1">
-        <v>3.9</v>
+        <v>-5.3</v>
       </c>
       <c r="M3" s="2">
-        <v>0.0045</v>
+        <v>-0.0061</v>
       </c>
       <c r="N3" s="1">
         <v>3.5</v>
@@ -657,7 +657,7 @@
         <v>3.5</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.0291</v>
+        <v>0.029</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
@@ -666,28 +666,28 @@
         <v>4</v>
       </c>
       <c r="T3" s="2">
-        <v>0.0028</v>
+        <v>-0.0079</v>
       </c>
       <c r="U3" s="5">
-        <v>2.167</v>
+        <v>2.144</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v/>
+        <v>0.0061</v>
       </c>
       <c r="X3" s="2">
-        <v>0.0183</v>
+        <v>0.0075</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0835</v>
+        <v>0.072</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0944</v>
+        <v>0.0828</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.1375</v>
+        <v>0.1255</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>743.6</v>
+        <v>733.7</v>
       </c>
       <c r="D4" s="1">
-        <v>8.8</v>
+        <v>-1.1</v>
       </c>
       <c r="E4" s="2">
-        <v>0.012</v>
+        <v>-0.0015</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,16 +719,16 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>6.5</v>
+        <v>-3.4</v>
       </c>
       <c r="K4" s="2">
-        <v>0.0088</v>
+        <v>-0.0046</v>
       </c>
       <c r="L4" s="1">
-        <v>6.5</v>
+        <v>-3.4</v>
       </c>
       <c r="M4" s="2">
-        <v>0.0088</v>
+        <v>-0.0046</v>
       </c>
       <c r="N4" s="1">
         <v>7.6</v>
@@ -740,7 +740,7 @@
         <v>7.6</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.025</v>
+        <v>0.0248</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>4</v>
       </c>
       <c r="T4" s="2">
-        <v>0.012</v>
+        <v>-0.0015</v>
       </c>
       <c r="U4" s="5">
-        <v>0.676</v>
+        <v>0.667</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v/>
+        <v>0.0045</v>
       </c>
       <c r="X4" s="2">
-        <v>0.0629</v>
+        <v>0.0487</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.065</v>
+        <v>-0.0775</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1856</v>
+        <v>-0.1964</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.0778</v>
+        <v>-0.0901</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>997.8</v>
+        <v>988.2</v>
       </c>
       <c r="D5" s="1">
-        <v>-5.6</v>
+        <v>-15.2</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.0056</v>
+        <v>-0.0151</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,25 +802,25 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>6.5</v>
+        <v>-3.1</v>
       </c>
       <c r="K5" s="2">
-        <v>0.0066</v>
+        <v>-0.0031</v>
       </c>
       <c r="L5" s="1">
-        <v>6.5</v>
+        <v>-3.1</v>
       </c>
       <c r="M5" s="2">
-        <v>0.0066</v>
+        <v>-0.0031</v>
       </c>
       <c r="N5" s="1">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="O5" s="1">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="P5" s="1">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="Q5" s="2">
         <v>0.0335</v>
@@ -832,28 +832,28 @@
         <v>4</v>
       </c>
       <c r="T5" s="2">
-        <v>-0.0056</v>
+        <v>-0.0151</v>
       </c>
       <c r="U5" s="5">
-        <v>4.989</v>
+        <v>4.941</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v/>
+        <v>0.0032</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0725</v>
+        <v>0.0622</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0681</v>
+        <v>0.0578</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0637</v>
+        <v>0.0535</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.3105</v>
+        <v>0.2979</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>978.2</v>
+        <v>979.5</v>
       </c>
       <c r="D6" s="1">
-        <v>-2.2</v>
+        <v>-0.9</v>
       </c>
       <c r="E6" s="2">
-        <v>-0.0022</v>
+        <v>-0.0009</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,28 +885,28 @@
         <v/>
       </c>
       <c r="J6" s="1">
+        <v>5.8</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0.006</v>
+      </c>
+      <c r="L6" s="1">
+        <v>5.8</v>
+      </c>
+      <c r="M6" s="2">
+        <v>0.006</v>
+      </c>
+      <c r="N6" s="1">
         <v>4.5</v>
       </c>
-      <c r="K6" s="2">
-        <v>0.0046</v>
-      </c>
-      <c r="L6" s="1">
+      <c r="O6" s="1">
         <v>4.5</v>
       </c>
-      <c r="M6" s="2">
-        <v>0.0046</v>
-      </c>
-      <c r="N6" s="1">
-        <v>4.2</v>
-      </c>
-      <c r="O6" s="1">
-        <v>4.2</v>
-      </c>
       <c r="P6" s="1">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.0329</v>
+        <v>0.0332</v>
       </c>
       <c r="R6" s="3">
         <v>100</v>
@@ -915,10 +915,10 @@
         <v>4</v>
       </c>
       <c r="T6" s="2">
-        <v>-0.0022</v>
+        <v>-0.0009</v>
       </c>
       <c r="U6" s="5">
-        <v>9.782</v>
+        <v>9.795</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
@@ -927,16 +927,16 @@
         <v/>
       </c>
       <c r="X6" s="2">
-        <v>-0.0143</v>
+        <v>-0.013</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.075</v>
+        <v>-0.0738</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0662</v>
+        <v>0.0676</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.3342</v>
+        <v>0.336</v>
       </c>
     </row>
     <row r="7">
@@ -947,37 +947,37 @@
         <v>中欧纯债</v>
       </c>
       <c r="C7" s="1">
-        <v>3021.3</v>
+        <v>3018.6</v>
       </c>
       <c r="D7" s="1">
+        <v>-2.7</v>
+      </c>
+      <c r="E7" s="2">
+        <v>-0.0009</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" s="2">
+        <v/>
+      </c>
+      <c r="H7" s="1">
+        <v/>
+      </c>
+      <c r="I7" s="2">
+        <v/>
+      </c>
+      <c r="J7" s="1">
+        <v>-0.15</v>
+      </c>
+      <c r="K7" s="2">
         <v>0</v>
       </c>
-      <c r="E7" s="2">
+      <c r="L7" s="1">
+        <v>-0.15</v>
+      </c>
+      <c r="M7" s="2">
         <v>0</v>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" s="2">
-        <v/>
-      </c>
-      <c r="H7" s="1">
-        <v/>
-      </c>
-      <c r="I7" s="2">
-        <v/>
-      </c>
-      <c r="J7" s="1">
-        <v>2.55</v>
-      </c>
-      <c r="K7" s="2">
-        <v>0.0008</v>
-      </c>
-      <c r="L7" s="1">
-        <v>2.55</v>
-      </c>
-      <c r="M7" s="2">
-        <v>0.0008</v>
       </c>
       <c r="N7" s="1">
         <v>2.55</v>
@@ -989,7 +989,7 @@
         <v>2.55</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1015</v>
+        <v>0.1022</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -998,10 +998,10 @@
         <v>4</v>
       </c>
       <c r="T7" s="2">
-        <v>0</v>
+        <v>-0.0009</v>
       </c>
       <c r="U7" s="5">
-        <v>1.119</v>
+        <v>1.118</v>
       </c>
       <c r="V7" s="5">
         <v>1.118</v>
@@ -1010,16 +1010,16 @@
         <v/>
       </c>
       <c r="X7" s="2">
-        <v>0.0036</v>
+        <v>0.0027</v>
       </c>
       <c r="Y7" s="2">
-        <v>0.0081</v>
+        <v>0.0072</v>
       </c>
       <c r="Z7" s="2">
-        <v>0.0108</v>
+        <v>0.0099</v>
       </c>
       <c r="AA7" s="2">
-        <v>0.0216</v>
+        <v>0.0207</v>
       </c>
     </row>
     <row r="8">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>804.6</v>
+        <v>792.2</v>
       </c>
       <c r="D8" s="1">
-        <v>-5</v>
+        <v>-17.4</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.0062</v>
+        <v>-0.0215</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>17.9</v>
+        <v>5.5</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0228</v>
+        <v>0.007</v>
       </c>
       <c r="L8" s="1">
-        <v>17.9</v>
+        <v>5.5</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0228</v>
+        <v>0.007</v>
       </c>
       <c r="N8" s="1">
-        <v>18.1</v>
+        <v>17.3</v>
       </c>
       <c r="O8" s="1">
-        <v>18.1</v>
+        <v>17.3</v>
       </c>
       <c r="P8" s="1">
-        <v>18.1</v>
+        <v>17.3</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.027</v>
+        <v>0.0268</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,10 +1081,10 @@
         <v>4</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.0062</v>
+        <v>-0.0215</v>
       </c>
       <c r="U8" s="5">
-        <v>4.023</v>
+        <v>3.961</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.16</v>
+        <v>0.1421</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.2321</v>
+        <v>0.2132</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2643</v>
+        <v>0.2449</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9818</v>
+        <v>0.9512</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>20106.8</v>
+        <v>19923.4</v>
       </c>
       <c r="D9" s="1">
-        <v>-113.4</v>
+        <v>-296.8</v>
       </c>
       <c r="E9" s="2">
-        <v>-0.0056</v>
+        <v>-0.0147</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,16 +1134,16 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-270.84</v>
+        <v>-454.24</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0133</v>
+        <v>-0.0223</v>
       </c>
       <c r="L9" s="1">
-        <v>-270.84</v>
+        <v>-454.24</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0133</v>
+        <v>-0.0223</v>
       </c>
       <c r="N9" s="1">
         <v>-269.44</v>
@@ -1155,7 +1155,7 @@
         <v>-269.44</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6754</v>
+        <v>0.6747</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>4</v>
       </c>
       <c r="T9" s="2">
-        <v>-0.0056</v>
+        <v>-0.0147</v>
       </c>
       <c r="U9" s="5">
-        <v>14.362</v>
+        <v>14.231</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0134</v>
+        <v>0.0228</v>
       </c>
       <c r="X9" s="2">
-        <v>0.0313</v>
+        <v>0.0219</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0175</v>
+        <v>-0.0265</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.045</v>
+        <v>0.0355</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1942</v>
+        <v>0.1833</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>652.4</v>
+        <v>650.8</v>
       </c>
       <c r="D10" s="1">
-        <v>-7.6</v>
+        <v>-9.2</v>
       </c>
       <c r="E10" s="2">
-        <v>-0.0115</v>
+        <v>-0.0139</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,28 +1217,28 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-19.7</v>
+        <v>-21.3</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0293</v>
+        <v>-0.0317</v>
       </c>
       <c r="L10" s="1">
-        <v>-19.7</v>
+        <v>-21.3</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0293</v>
+        <v>-0.0317</v>
       </c>
       <c r="N10" s="1">
-        <v>-19.7</v>
+        <v>-20.1</v>
       </c>
       <c r="O10" s="1">
-        <v>-19.7</v>
+        <v>-20.1</v>
       </c>
       <c r="P10" s="1">
-        <v>-19.7</v>
+        <v>-20.1</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.0219</v>
+        <v>0.022</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1247,28 +1247,28 @@
         <v>4</v>
       </c>
       <c r="T10" s="2">
-        <v>-0.0115</v>
+        <v>-0.0139</v>
       </c>
       <c r="U10" s="5">
-        <v>1.631</v>
+        <v>1.627</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.03</v>
+        <v>0.0326</v>
       </c>
       <c r="X10" s="2">
-        <v>0.0037</v>
+        <v>0.0012</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.2852</v>
+        <v>0.2821</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3292</v>
+        <v>0.326</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.2441</v>
+        <v>0.2411</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>878.8</v>
+        <v>871.6</v>
       </c>
       <c r="D11" s="1">
-        <v>-5.6</v>
+        <v>-12.8</v>
       </c>
       <c r="E11" s="2">
-        <v>-0.0063</v>
+        <v>-0.0145</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,16 +1300,16 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>18.3</v>
+        <v>11.1</v>
       </c>
       <c r="K11" s="2">
-        <v>0.0213</v>
+        <v>0.0129</v>
       </c>
       <c r="L11" s="1">
-        <v>18.3</v>
+        <v>11.1</v>
       </c>
       <c r="M11" s="2">
-        <v>0.0213</v>
+        <v>0.0129</v>
       </c>
       <c r="N11" s="1">
         <v>18.7</v>
@@ -1330,10 +1330,10 @@
         <v>4</v>
       </c>
       <c r="T11" s="2">
-        <v>-0.0063</v>
+        <v>-0.0145</v>
       </c>
       <c r="U11" s="5">
-        <v>2.197</v>
+        <v>2.179</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
@@ -1342,16 +1342,16 @@
         <v/>
       </c>
       <c r="X11" s="2">
-        <v>0.0686</v>
+        <v>0.0598</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0707</v>
+        <v>0.0619</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.1973</v>
+        <v>0.1875</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.3132</v>
+        <v>0.3025</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29764.1</v>
+        <v>29521.4</v>
       </c>
       <c r="D12" s="1">
-        <v>-134</v>
+        <v>-376.7</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.0045</v>
+        <v>-0.0126</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-227.69</v>
+        <v>-470.39</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0076</v>
+        <v>-0.0157</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-225.49</v>
+        <v>-226.99</v>
       </c>
       <c r="O12" s="1">
-        <v>-225.49</v>
+        <v>-226.99</v>
       </c>
       <c r="P12" s="1">
-        <v>-225.49</v>
+        <v>-226.99</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9997</v>
